--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.51614785146993</v>
+        <v>7.396374025863864</v>
       </c>
       <c r="D2" t="n">
-        <v>45.61598731345834</v>
+        <v>7.41259793843698</v>
       </c>
       <c r="E2" t="n">
-        <v>9.666467718246032</v>
+        <v>1.57080100421498</v>
       </c>
       <c r="F2" t="n">
-        <v>9.736241045934372</v>
+        <v>1.582139169964336</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.0023925139019</v>
+        <v>8.612888783509058</v>
       </c>
       <c r="D3" t="n">
-        <v>52.95423919942538</v>
+        <v>8.605063869906624</v>
       </c>
       <c r="E3" t="n">
-        <v>9.666467718246032</v>
+        <v>1.57080100421498</v>
       </c>
       <c r="F3" t="n">
-        <v>9.736241045934372</v>
+        <v>1.582139169964336</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.92490341221602</v>
+        <v>6.487796804485103</v>
       </c>
       <c r="D4" t="n">
-        <v>39.81553882244283</v>
+        <v>6.470025058646959</v>
       </c>
       <c r="E4" t="n">
-        <v>9.666467718246032</v>
+        <v>1.57080100421498</v>
       </c>
       <c r="F4" t="n">
-        <v>9.736241045934372</v>
+        <v>1.582139169964336</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.81253322974078</v>
+        <v>5.494536649832876</v>
       </c>
       <c r="D5" t="n">
-        <v>33.68972966614983</v>
+        <v>5.474581070749347</v>
       </c>
       <c r="E5" t="n">
-        <v>9.666467718246032</v>
+        <v>1.57080100421498</v>
       </c>
       <c r="F5" t="n">
-        <v>9.736241045934372</v>
+        <v>1.582139169964336</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.20110780694945</v>
+        <v>8.482680018629287</v>
       </c>
       <c r="D6" t="n">
-        <v>52.29935989217567</v>
+        <v>8.498645982478546</v>
       </c>
       <c r="E6" t="n">
-        <v>9.666467718246032</v>
+        <v>1.57080100421498</v>
       </c>
       <c r="F6" t="n">
-        <v>9.736241045934372</v>
+        <v>1.582139169964336</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.83846907427578</v>
+        <v>6.148751224569814</v>
       </c>
       <c r="D7" t="n">
-        <v>37.67954998266025</v>
+        <v>6.12292687218229</v>
       </c>
       <c r="E7" t="n">
-        <v>9.666467718246032</v>
+        <v>1.57080100421498</v>
       </c>
       <c r="F7" t="n">
-        <v>9.736241045934372</v>
+        <v>1.582139169964336</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>64.01502203832834</v>
+        <v>10.40244108122836</v>
       </c>
       <c r="D8" t="n">
-        <v>64.0746619747117</v>
+        <v>10.41213257089065</v>
       </c>
       <c r="E8" t="n">
-        <v>9.666467718246032</v>
+        <v>1.57080100421498</v>
       </c>
       <c r="F8" t="n">
-        <v>9.736241045934372</v>
+        <v>1.582139169964336</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>56.5219343547749</v>
+        <v>9.184814332650921</v>
       </c>
       <c r="D9" t="n">
-        <v>56.55473430833388</v>
+        <v>9.190144325104256</v>
       </c>
       <c r="E9" t="n">
-        <v>9.666467718246032</v>
+        <v>1.57080100421498</v>
       </c>
       <c r="F9" t="n">
-        <v>9.736241045934372</v>
+        <v>1.582139169964336</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
